--- a/BDD-practice US-TS-Risks-Priority-TCs.xlsx
+++ b/BDD-practice US-TS-Risks-Priority-TCs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\advanced_test\BDD-practice-project-pasztorz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\codecool\advanced_test\bdd-practice-project-pasztorz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253AAA0D-CCEE-4914-BEBD-124BFC611715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F028B2-F266-466E-809C-A0DF7F903767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{95AC660F-113D-4FB6-9BE7-F31DFAE2BEAF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>User Story</t>
   </si>
@@ -138,6 +138,15 @@
   </si>
   <si>
     <t>Log out from own profile is unsuccessful</t>
+  </si>
+  <si>
+    <t>Verify if Unregistered User cannot Log In</t>
+  </si>
+  <si>
+    <t>Log In with not registered credentials</t>
+  </si>
+  <si>
+    <t>Unregistered User can log in and use the system</t>
   </si>
 </sst>
 </file>
@@ -280,60 +289,60 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -670,15 +679,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F84833-6D16-495A-B8ED-624A28F1B719}">
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.77734375" customWidth="1"/>
     <col min="2" max="2" width="29.5546875" style="13" customWidth="1"/>
     <col min="3" max="3" width="29.5546875" style="11" customWidth="1"/>
-    <col min="4" max="4" width="4.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.33203125" style="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.33203125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="4.33203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.33203125" style="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.88671875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.5546875" style="11" customWidth="1"/>
     <col min="9" max="10" width="4.33203125" style="11" customWidth="1"/>
@@ -688,67 +697,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="26" t="s">
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="31" t="s">
+      <c r="A2" s="30"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31" t="s">
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="27"/>
-      <c r="M2" s="29"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="32"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="21"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="35"/>
       <c r="H3" s="16" t="s">
         <v>17</v>
       </c>
@@ -758,27 +767,27 @@
       <c r="J3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="29"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="32"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="25" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="19" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="12"/>
@@ -788,14 +797,14 @@
       <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="22"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="26"/>
       <c r="E5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G5" s="12"/>
@@ -805,20 +814,20 @@
       <c r="K5" s="12"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="19" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="25" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="25" t="s">
         <v>11</v>
       </c>
       <c r="G6" s="12"/>
@@ -828,14 +837,14 @@
       <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="22"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="26"/>
       <c r="E7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="22"/>
+      <c r="F7" s="26"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -843,14 +852,14 @@
       <c r="K7" s="12"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="22"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="26"/>
       <c r="E8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="22"/>
+      <c r="F8" s="26"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -858,14 +867,14 @@
       <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="22"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="26"/>
       <c r="E9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="22"/>
+      <c r="F9" s="26"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -873,66 +882,77 @@
       <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="22"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="26"/>
       <c r="E10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="22"/>
+      <c r="F10" s="26"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="32"/>
+    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="24"/>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>24</v>
+      </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>27</v>
-      </c>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="4"/>
       <c r="B12" s="2"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="32"/>
-      <c r="F12" s="32"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
+    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="32"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
+    <row r="14" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
       <c r="B14" s="2"/>
       <c r="C14" s="4"/>
-      <c r="D14" s="32"/>
-      <c r="F14" s="32"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
@@ -940,12 +960,11 @@
       <c r="K14" s="12"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="32"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>
       <c r="I15" s="12"/>
@@ -953,12 +972,12 @@
       <c r="K15" s="12"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="2"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="32"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="19"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="32"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
@@ -966,12 +985,12 @@
       <c r="K16" s="12"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="2"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="32"/>
+      <c r="D17" s="19"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="32"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
       <c r="I17" s="12"/>
@@ -979,12 +998,12 @@
       <c r="K17" s="12"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="2"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="32"/>
+      <c r="D18" s="19"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="32"/>
+      <c r="F18" s="19"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
@@ -992,12 +1011,12 @@
       <c r="K18" s="12"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="2"/>
       <c r="C19" s="4"/>
-      <c r="D19" s="32"/>
+      <c r="D19" s="19"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="32"/>
+      <c r="F19" s="19"/>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
       <c r="I19" s="12"/>
@@ -1005,277 +1024,278 @@
       <c r="K19" s="12"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="2"/>
       <c r="C20" s="4"/>
-      <c r="F20" s="32"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="19"/>
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:13" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="32"/>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="C21" s="4"/>
+      <c r="F21" s="19"/>
       <c r="G21" s="12"/>
       <c r="H21" s="12"/>
       <c r="I21" s="12"/>
       <c r="J21" s="12"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:13" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="22"/>
+    <row r="22" spans="1:13" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>11</v>
+      </c>
       <c r="E22" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="32"/>
+        <v>31</v>
+      </c>
+      <c r="F22" s="19"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="8"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="14"/>
+    </row>
+    <row r="23" spans="1:13" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="36"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="19"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="14"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="36"/>
+      <c r="D25" s="22"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="32"/>
+      <c r="F25" s="17"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="17"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="36"/>
+      <c r="D26" s="22"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="17"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="14"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="36"/>
+      <c r="D27" s="22"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="32"/>
+      <c r="F27" s="17"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="17"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="36"/>
+      <c r="D28" s="22"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="14"/>
       <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="17"/>
-    </row>
-    <row r="29" spans="1:13" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="14"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="36"/>
+      <c r="D29" s="22"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" spans="1:13" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="36"/>
+      <c r="D30" s="22"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="19"/>
       <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
       <c r="K30" s="18"/>
     </row>
-    <row r="31" spans="1:13" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="36"/>
+      <c r="D31" s="22"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="32"/>
+      <c r="F31" s="17"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="14"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="18"/>
+    </row>
+    <row r="32" spans="1:13" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="36"/>
+      <c r="D32" s="22"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="17"/>
+      <c r="F32" s="19"/>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="14"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="36"/>
-      <c r="F33" s="32"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="17"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="17"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="36"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+      <c r="D34" s="22"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="14"/>
       <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="17"/>
-    </row>
-    <row r="35" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="14"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="36"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="14"/>
+      <c r="D35" s="22"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="17"/>
     </row>
     <row r="36" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="36"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
+      <c r="D36" s="22"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="17"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="14"/>
+    </row>
+    <row r="37" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="14"/>
+      <c r="D37" s="22"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="14"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="17"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="32"/>
+      <c r="D38" s="19"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="14"/>
       <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="14"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="17"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="17"/>
-      <c r="F40" s="32"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="19"/>
+      <c r="F40" s="19"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
       <c r="I40" s="12"/>
@@ -1283,47 +1303,47 @@
       <c r="K40" s="12"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="17"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="9"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="7"/>
+      <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="2"/>
       <c r="C46" s="12"/>
-      <c r="D46" s="32"/>
-      <c r="F46" s="32"/>
+      <c r="D46" s="19"/>
+      <c r="F46" s="19"/>
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
@@ -1333,48 +1353,57 @@
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
       <c r="B47" s="2"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
+      <c r="B48" s="2"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="35"/>
-      <c r="F48" s="35"/>
+      <c r="D48" s="21"/>
+      <c r="F48" s="21"/>
       <c r="G48" s="15"/>
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
       <c r="J48" s="15"/>
       <c r="K48" s="15"/>
     </row>
-    <row r="49" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C49" s="5"/>
+      <c r="D49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+    </row>
+    <row r="50" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12"/>
-      <c r="K51" s="12"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
@@ -1391,14 +1420,18 @@
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
     </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="F6:F10"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="D6:D10"/>
-    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="A4:A11"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="L1:L3"/>
     <mergeCell ref="M1:M3"/>
@@ -1411,12 +1444,11 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="K2:K3"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="F6:F10"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="D6:D10"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
